--- a/PET_Diagnostic_Clip/Rev. 3/Excel/PETDiag_Clip_BOM_v3_0.xlsx
+++ b/PET_Diagnostic_Clip/Rev. 3/Excel/PETDiag_Clip_BOM_v3_0.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Projekte\_Eigene\PET_CBM_Projects\PET_Diagostics\PET_Diagnostic_Clip\Rev. 3\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E82B2C-F131-45BA-B5C5-4FB8A70353EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50A886C-6A59-488F-B509-4CD98A232B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="696" yWindow="2304" windowWidth="30024" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3780" yWindow="108" windowWidth="27036" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stückliste" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Stückliste!$A$1:$F$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Stückliste!$A$1:$F$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Stückliste!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="72">
   <si>
     <t>Pos.</t>
   </si>
@@ -218,9 +218,6 @@
     <t>PCB Rev. 3</t>
   </si>
   <si>
-    <t xml:space="preserve">external DPDT switch </t>
-  </si>
-  <si>
     <t>Reichelt.de: T217 or AliExpress SS22F25-G7</t>
   </si>
   <si>
@@ -228,19 +225,40 @@
   </si>
   <si>
     <t>JP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPDT switch </t>
+  </si>
+  <si>
+    <t>3D printed case</t>
+  </si>
+  <si>
+    <t>Rev. 3</t>
+  </si>
+  <si>
+    <t>C2.9x9.5H</t>
+  </si>
+  <si>
+    <t>self tapping screws, DIN7981 (dia 2.9mm, length 9.5mm)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Futura Lt BT"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -706,49 +724,49 @@
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -756,10 +774,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -771,8 +789,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -786,23 +810,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -984,8 +1008,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabelle1" displayName="Tabelle1" ref="A3:F20" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
-  <autoFilter ref="A3:F20" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabelle1" displayName="Tabelle1" ref="A3:F22" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="A3:F22" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:F34">
     <sortCondition ref="E3:E34"/>
   </sortState>
@@ -1312,24 +1336,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
     </row>
     <row r="2" spans="1:6" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -1358,13 +1382,13 @@
       <c r="B4" s="3">
         <v>1</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="16" t="s">
         <v>62</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="16" t="s">
         <v>63</v>
       </c>
       <c r="F4" s="11" t="s">
@@ -1379,17 +1403,17 @@
       <c r="B5" s="3">
         <v>1</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>64</v>
+      <c r="C5" s="17" t="s">
+        <v>67</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="F5" s="18" t="s">
-        <v>65</v>
+      <c r="F5" s="16" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="6" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
@@ -1448,8 +1472,8 @@
       <c r="D8" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="18" t="s">
-        <v>66</v>
+      <c r="E8" s="16" t="s">
+        <v>65</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>37</v>
@@ -1616,8 +1640,8 @@
       <c r="D16" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="E16" s="18" t="s">
-        <v>67</v>
+      <c r="E16" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>42</v>
@@ -1669,7 +1693,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" s="13" t="s">
         <v>56</v>
@@ -1698,20 +1722,38 @@
       </c>
     </row>
     <row r="21" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
+      <c r="A21" s="17">
+        <f>A20+1</f>
+        <v>18</v>
+      </c>
+      <c r="B21" s="17">
+        <v>1</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="18"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="22" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
+      <c r="A22" s="17">
+        <f>A21+1</f>
+        <v>19</v>
+      </c>
+      <c r="B22" s="17">
+        <v>4</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="18"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="23" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
